--- a/02_dynein_KDs/TableS5_dynein_KDs.xlsx
+++ b/02_dynein_KDs/TableS5_dynein_KDs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/nalytorres/Documents/GitHub/ERM1_TorresMangual/02_dynein_KDs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBB9BDEF-5894-EB43-AC71-719A5D19FF4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CEAB5B9-1736-EC42-8D3C-F86764CB3825}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7200" yWindow="660" windowWidth="23040" windowHeight="17440" xr2:uid="{2E47865C-5B6A-2C4D-BA8F-0F652FA7F24F}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="210">
   <si>
     <t>Description</t>
   </si>
@@ -637,6 +637,89 @@
   </si>
   <si>
     <t>true location shift ≠ 0</t>
+  </si>
+  <si>
+    <t>unique identifier of image: date_misc_strain_treatment_imageNumber</t>
+  </si>
+  <si>
+    <t>total number of spots per embryo - as reported with WormLib</t>
+  </si>
+  <si>
+    <t>longer image ID. Redundant with above</t>
+  </si>
+  <si>
+    <t>treatment condition</t>
+  </si>
+  <si>
+    <t>mRNA species observed by smFISH</t>
+  </si>
+  <si>
+    <t>mean total number of mRNA molecules per embryo averaged across all embryos</t>
+  </si>
+  <si>
+    <t>standard deviation of the mean above</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>The mRNA species being tested (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>set3_mRNA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+        <family val="2"/>
+      </rPr>
+      <t>erm1_mRNA</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> — total molecule counts).</t>
+    </r>
+  </si>
+  <si>
+    <t>Wilcoxon rank sum test (Mann-Whitney U), a non-parametric test comparing distributions between two groups.</t>
+  </si>
+  <si>
+    <t>The Wilcoxon test statistic, based on the sum of ranks; used to compute the p-value.</t>
+  </si>
+  <si>
+    <t>Specifies a two-sided test — checking whether the true location (median) shift between groups is different from zero, in either direction.</t>
+  </si>
+  <si>
+    <t>Probability of observing a difference this extreme if there were truly no difference between groups.</t>
   </si>
 </sst>
 </file>
@@ -644,9 +727,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.000E+00"/>
+    <numFmt numFmtId="164" formatCode="0.000E+00"/>
   </numFmts>
-  <fonts count="17" x14ac:knownFonts="1">
+  <fonts count="19">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -764,6 +847,19 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Lucida Sans"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -832,6 +928,28 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -841,30 +959,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1199,121 +1295,121 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FF4FD9A-8CC9-294A-86D4-1970C3AC1875}">
-  <dimension ref="A1:D38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="3" max="3" width="13.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="27" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="27">
       <c r="A1" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
     </row>
-    <row r="2" spans="1:4" ht="25" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" ht="25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" ht="20">
       <c r="A4" s="3" t="s">
         <v>1</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4">
       <c r="A5" s="4"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4">
       <c r="A6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="5"/>
       <c r="C6" s="5"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4">
       <c r="A7" s="5"/>
       <c r="B7" s="5"/>
       <c r="C7" s="5"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4">
       <c r="A8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="5"/>
       <c r="C8" s="5"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4">
       <c r="A9" s="5"/>
       <c r="B9" s="5"/>
       <c r="C9" s="5"/>
     </row>
-    <row r="10" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" ht="20">
       <c r="A10" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C10" s="16"/>
+      <c r="C10" s="24"/>
       <c r="D10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4">
       <c r="A11" s="6"/>
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="17"/>
+      <c r="C11" s="25"/>
       <c r="D11" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4">
       <c r="A12" s="5"/>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="C12" s="16"/>
+      <c r="C12" s="24"/>
       <c r="D12" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4">
       <c r="A14" s="6"/>
       <c r="B14" s="6"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" ht="20">
       <c r="A15" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B15" s="10"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="16" t="s">
+    <row r="16" spans="1:4">
+      <c r="A16" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B16" s="16"/>
+      <c r="B16" s="24"/>
       <c r="C16" s="8" t="s">
         <v>7</v>
       </c>
@@ -1321,68 +1417,86 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="18" t="s">
+    <row r="17" spans="1:9">
+      <c r="A17" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="18"/>
+      <c r="B17" s="26"/>
       <c r="C17" s="1" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="18" t="s">
+      <c r="D17" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="B18" s="18"/>
+      <c r="B18" s="26"/>
       <c r="C18" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="D18" s="1"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="18" t="s">
+      <c r="D18" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H18" s="27"/>
+      <c r="I18" s="27"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B19" s="18"/>
+      <c r="B19" s="26"/>
       <c r="C19" s="15" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A20" s="18" t="s">
+      <c r="D19" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="B20" s="18"/>
+      <c r="B20" s="26"/>
       <c r="C20" s="1" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="18" t="s">
+      <c r="D20" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" s="26" t="s">
         <v>19</v>
       </c>
-      <c r="B21" s="18"/>
+      <c r="B21" s="26"/>
       <c r="C21" s="1" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A22" s="18"/>
-      <c r="B22" s="18"/>
+      <c r="D21" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="24" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+    <row r="24" spans="1:9" ht="20">
+      <c r="A24" s="23" t="s">
         <v>5</v>
       </c>
-      <c r="B24" s="19"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="16" t="s">
+      <c r="B24" s="23"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B25" s="16"/>
+      <c r="B25" s="24"/>
       <c r="C25" s="8" t="s">
         <v>7</v>
       </c>
@@ -1390,7 +1504,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9">
       <c r="A26" t="s">
         <v>19</v>
       </c>
@@ -1398,87 +1512,117 @@
       <c r="C26" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D26" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
       <c r="A27" t="s">
         <v>184</v>
       </c>
       <c r="C27" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="28" spans="1:4" ht="20" x14ac:dyDescent="0.25">
-      <c r="A28" s="20" t="s">
+      <c r="D27" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="20">
+      <c r="A28" t="s">
         <v>185</v>
       </c>
       <c r="B28" s="10"/>
       <c r="C28" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="20" t="s">
+      <c r="D28" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
         <v>186</v>
       </c>
       <c r="C29" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="D29" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
       <c r="A30" s="12"/>
     </row>
-    <row r="32" spans="1:4" ht="20" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:9" ht="20">
       <c r="A32" s="10" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4">
       <c r="A33" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C33" s="8" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A34" s="26" t="s">
+      <c r="D33" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="17">
+      <c r="A34" s="20" t="s">
         <v>191</v>
       </c>
       <c r="C34" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A35" s="26" t="s">
+      <c r="D34" s="28" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="20" t="s">
         <v>192</v>
       </c>
       <c r="C35" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A36" s="26" t="s">
+      <c r="D35" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="20" t="s">
         <v>193</v>
       </c>
       <c r="C36" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A37" s="26" t="s">
+      <c r="D36" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="20" t="s">
         <v>194</v>
       </c>
       <c r="C37" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="38" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="27" t="s">
+      <c r="D37" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="30" customHeight="1">
+      <c r="A38" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="B38" s="28"/>
+      <c r="B38" s="22"/>
       <c r="C38" t="s">
         <v>187</v>
+      </c>
+      <c r="D38" t="s">
+        <v>208</v>
       </c>
     </row>
   </sheetData>
@@ -1504,13 +1648,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A46F1505-F7F2-7349-822C-7CE1A7E41879}">
   <dimension ref="A1:E81"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.5" customWidth="1"/>
     <col min="4" max="4" width="48.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="13" t="s">
         <v>15</v>
       </c>
@@ -1527,7 +1671,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="A2" s="13" t="s">
         <v>20</v>
       </c>
@@ -1544,7 +1688,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3" s="13" t="s">
         <v>23</v>
       </c>
@@ -1561,7 +1705,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4" s="13" t="s">
         <v>25</v>
       </c>
@@ -1578,7 +1722,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5" s="13" t="s">
         <v>27</v>
       </c>
@@ -1595,7 +1739,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6" s="13" t="s">
         <v>29</v>
       </c>
@@ -1612,7 +1756,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" s="13" t="s">
         <v>31</v>
       </c>
@@ -1629,7 +1773,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" s="13" t="s">
         <v>33</v>
       </c>
@@ -1646,7 +1790,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" s="13" t="s">
         <v>35</v>
       </c>
@@ -1663,7 +1807,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" s="13" t="s">
         <v>37</v>
       </c>
@@ -1680,7 +1824,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5">
       <c r="A11" s="13" t="s">
         <v>39</v>
       </c>
@@ -1697,7 +1841,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5">
       <c r="A12" s="13" t="s">
         <v>41</v>
       </c>
@@ -1714,7 +1858,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5">
       <c r="A13" s="13" t="s">
         <v>43</v>
       </c>
@@ -1731,7 +1875,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5">
       <c r="A14" s="13" t="s">
         <v>45</v>
       </c>
@@ -1748,7 +1892,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5">
       <c r="A15" s="13" t="s">
         <v>47</v>
       </c>
@@ -1765,7 +1909,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5">
       <c r="A16" s="13" t="s">
         <v>49</v>
       </c>
@@ -1782,7 +1926,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5">
       <c r="A17" s="13" t="s">
         <v>51</v>
       </c>
@@ -1799,7 +1943,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5">
       <c r="A18" s="13" t="s">
         <v>53</v>
       </c>
@@ -1816,7 +1960,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5">
       <c r="A19" s="13" t="s">
         <v>55</v>
       </c>
@@ -1833,7 +1977,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5">
       <c r="A20" s="13" t="s">
         <v>57</v>
       </c>
@@ -1850,7 +1994,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5">
       <c r="A21" s="13" t="s">
         <v>59</v>
       </c>
@@ -1867,7 +2011,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5">
       <c r="A22" s="13" t="s">
         <v>61</v>
       </c>
@@ -1884,7 +2028,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5">
       <c r="A23" s="13" t="s">
         <v>63</v>
       </c>
@@ -1901,7 +2045,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5">
       <c r="A24" s="13" t="s">
         <v>65</v>
       </c>
@@ -1918,7 +2062,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5">
       <c r="A25" s="13" t="s">
         <v>67</v>
       </c>
@@ -1935,7 +2079,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5">
       <c r="A26" s="13" t="s">
         <v>69</v>
       </c>
@@ -1952,7 +2096,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:5">
       <c r="A27" s="13" t="s">
         <v>71</v>
       </c>
@@ -1969,7 +2113,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:5">
       <c r="A28" s="13" t="s">
         <v>73</v>
       </c>
@@ -1986,7 +2130,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:5">
       <c r="A29" s="13" t="s">
         <v>75</v>
       </c>
@@ -2003,7 +2147,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:5">
       <c r="A30" s="13" t="s">
         <v>77</v>
       </c>
@@ -2020,7 +2164,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:5">
       <c r="A31" s="13" t="s">
         <v>79</v>
       </c>
@@ -2037,7 +2181,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:5">
       <c r="A32" s="13" t="s">
         <v>81</v>
       </c>
@@ -2054,7 +2198,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:5">
       <c r="A33" s="13" t="s">
         <v>83</v>
       </c>
@@ -2071,7 +2215,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:5">
       <c r="A34" s="13" t="s">
         <v>85</v>
       </c>
@@ -2088,7 +2232,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:5">
       <c r="A35" s="13" t="s">
         <v>87</v>
       </c>
@@ -2105,7 +2249,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:5">
       <c r="A36" s="13" t="s">
         <v>89</v>
       </c>
@@ -2122,7 +2266,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:5">
       <c r="A37" s="13" t="s">
         <v>91</v>
       </c>
@@ -2139,7 +2283,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:5">
       <c r="A38" s="13" t="s">
         <v>93</v>
       </c>
@@ -2156,7 +2300,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:5">
       <c r="A39" s="13" t="s">
         <v>95</v>
       </c>
@@ -2173,7 +2317,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:5">
       <c r="A40" s="13" t="s">
         <v>97</v>
       </c>
@@ -2190,7 +2334,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:5">
       <c r="A41" s="13" t="s">
         <v>99</v>
       </c>
@@ -2207,7 +2351,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:5">
       <c r="A42" s="13" t="s">
         <v>101</v>
       </c>
@@ -2224,7 +2368,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:5">
       <c r="A43" s="13" t="s">
         <v>103</v>
       </c>
@@ -2241,7 +2385,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:5">
       <c r="A44" s="13" t="s">
         <v>105</v>
       </c>
@@ -2258,7 +2402,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:5">
       <c r="A45" s="13" t="s">
         <v>107</v>
       </c>
@@ -2275,7 +2419,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:5">
       <c r="A46" s="13" t="s">
         <v>109</v>
       </c>
@@ -2292,7 +2436,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:5">
       <c r="A47" s="13" t="s">
         <v>111</v>
       </c>
@@ -2309,7 +2453,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:5">
       <c r="A48" s="13" t="s">
         <v>113</v>
       </c>
@@ -2326,7 +2470,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:5">
       <c r="A49" s="13" t="s">
         <v>115</v>
       </c>
@@ -2343,7 +2487,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:5">
       <c r="A50" s="13" t="s">
         <v>117</v>
       </c>
@@ -2360,7 +2504,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:5">
       <c r="A51" s="13" t="s">
         <v>119</v>
       </c>
@@ -2377,7 +2521,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:5">
       <c r="A52" s="13" t="s">
         <v>121</v>
       </c>
@@ -2394,7 +2538,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:5">
       <c r="A53" s="13" t="s">
         <v>123</v>
       </c>
@@ -2411,7 +2555,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:5">
       <c r="A54" s="13" t="s">
         <v>125</v>
       </c>
@@ -2428,7 +2572,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:5">
       <c r="A55" s="13" t="s">
         <v>127</v>
       </c>
@@ -2445,7 +2589,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:5">
       <c r="A56" s="13" t="s">
         <v>129</v>
       </c>
@@ -2462,7 +2606,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:5">
       <c r="A57" s="13" t="s">
         <v>131</v>
       </c>
@@ -2479,7 +2623,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:5">
       <c r="A58" s="13" t="s">
         <v>133</v>
       </c>
@@ -2496,7 +2640,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:5">
       <c r="A59" s="13" t="s">
         <v>135</v>
       </c>
@@ -2513,7 +2657,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:5">
       <c r="A60" s="13" t="s">
         <v>138</v>
       </c>
@@ -2530,7 +2674,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:5">
       <c r="A61" s="13" t="s">
         <v>140</v>
       </c>
@@ -2547,7 +2691,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:5">
       <c r="A62" s="13" t="s">
         <v>142</v>
       </c>
@@ -2564,7 +2708,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:5">
       <c r="A63" s="13" t="s">
         <v>144</v>
       </c>
@@ -2581,7 +2725,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:5">
       <c r="A64" s="13" t="s">
         <v>146</v>
       </c>
@@ -2598,7 +2742,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:5">
       <c r="A65" s="13" t="s">
         <v>148</v>
       </c>
@@ -2615,7 +2759,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:5">
       <c r="A66" s="13" t="s">
         <v>150</v>
       </c>
@@ -2632,7 +2776,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:5">
       <c r="A67" s="13" t="s">
         <v>152</v>
       </c>
@@ -2649,7 +2793,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:5">
       <c r="A68" s="13" t="s">
         <v>154</v>
       </c>
@@ -2666,7 +2810,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:5">
       <c r="A69" s="13" t="s">
         <v>156</v>
       </c>
@@ -2683,7 +2827,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:5">
       <c r="A70" s="13" t="s">
         <v>158</v>
       </c>
@@ -2700,7 +2844,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:5">
       <c r="A71" s="13" t="s">
         <v>160</v>
       </c>
@@ -2717,7 +2861,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:5">
       <c r="A72" s="13" t="s">
         <v>162</v>
       </c>
@@ -2734,7 +2878,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:5">
       <c r="A73" s="13" t="s">
         <v>164</v>
       </c>
@@ -2751,7 +2895,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:5">
       <c r="A74" s="13" t="s">
         <v>166</v>
       </c>
@@ -2768,7 +2912,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:5">
       <c r="A75" s="13" t="s">
         <v>168</v>
       </c>
@@ -2785,7 +2929,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:5">
       <c r="A76" s="13" t="s">
         <v>170</v>
       </c>
@@ -2802,7 +2946,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:5">
       <c r="A77" s="13" t="s">
         <v>172</v>
       </c>
@@ -2819,7 +2963,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:5">
       <c r="A78" s="13" t="s">
         <v>174</v>
       </c>
@@ -2836,7 +2980,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:5">
       <c r="A79" s="13" t="s">
         <v>176</v>
       </c>
@@ -2853,7 +2997,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:5">
       <c r="A80" s="13" t="s">
         <v>178</v>
       </c>
@@ -2870,7 +3014,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:5">
       <c r="A81" s="13" t="s">
         <v>180</v>
       </c>
@@ -2895,9 +3039,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C168F5A-E815-0A44-A305-F0599336BDA7}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>19</v>
       </c>
@@ -2911,7 +3055,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5">
       <c r="B2" t="s">
         <v>187</v>
       </c>
@@ -2925,7 +3069,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -2942,7 +3086,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -2959,7 +3103,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -2976,7 +3120,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -3000,62 +3144,61 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A9D46D0-A071-5E48-B8F9-D959A7777A3E}">
-  <dimension ref="A1:F3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:E3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="27.5" customWidth="1"/>
     <col min="5" max="5" width="31.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:5">
+      <c r="A1" s="19" t="s">
         <v>191</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="19" t="s">
         <v>192</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="19" t="s">
         <v>193</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="19" t="s">
         <v>194</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="19" t="s">
         <v>195</v>
       </c>
-      <c r="F1" s="25"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A2" s="21" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="16" t="s">
         <v>189</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="C2" s="22">
+      <c r="C2" s="17">
         <v>1096</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="18">
         <v>2.9040000000000001E-6</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="16" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A3" s="21" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="16" t="s">
         <v>190</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="17">
         <v>1160</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="18">
         <v>8.4279999999999998E-8</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="16" t="s">
         <v>197</v>
       </c>
     </row>
@@ -3065,6 +3208,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008D551129DB99E8438FE6EF309F08C354" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7dc744bdf5b6a0bc20f5fdcb351cc095">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="12423bc7-10a6-4cd4-bb27-11b0289f8e4d" xmlns:ns3="17c61571-0fe9-4ceb-9b66-2de528a072b1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3890b32a57b45779b4d4b2e999852729" ns2:_="" ns3:_="">
     <xsd:import namespace="12423bc7-10a6-4cd4-bb27-11b0289f8e4d"/>
@@ -3277,15 +3429,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -3298,6 +3441,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{349E94C1-8144-465E-BEF6-F5255DE36DE4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E34AA185-27E2-43D0-9F42-CE10CD9A7418}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3312,14 +3463,6 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
     <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{349E94C1-8144-465E-BEF6-F5255DE36DE4}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
